--- a/oPool_display/experimental_data/validation/BLI/oPool_competition_validation/oPool_competition_validation_sample_names.xlsx
+++ b/oPool_display/experimental_data/validation/BLI/oPool_competition_validation/oPool_competition_validation_sample_names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/owenouyang/Desktop/Git_Repo/oPool_display/oPool_display/experimental_data/validation/BLI/oPool_competition_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A02DCA-7EC8-D44F-B571-CF09686500C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A30CA24-2B4F-0E41-BB77-AB4552F1C8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39400" yWindow="1980" windowWidth="20280" windowHeight="17440" xr2:uid="{AA0690F2-11C0-B342-945D-36AF2DF8266B}"/>
   </bookViews>
@@ -122,75 +122,39 @@
     <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/B1.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/F1.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/B7.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/F7.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/A1.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/E1.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/C7.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/G7.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/A7.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/E7.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/D7.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06/H7.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/A4.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/E4.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/B3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/F3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/C3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/G3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/A3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/E3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/D3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/H3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/B4.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15/F4.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/QH_H5/A7.xls</t>
   </si>
   <si>
@@ -230,55 +194,91 @@
     <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/C2.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/G1.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/B2.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/F1.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/A2.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/E1.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/D1.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13/H1.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/D3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/H3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/C3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/G3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/B3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/F3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/A3.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/E3.xls</t>
-  </si>
-  <si>
     <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/B5.xls</t>
   </si>
   <si>
-    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40/F5.xls</t>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06_H1/F1.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06_H1/F7.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06_H1/E1.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06_H1/G7.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06_H1/E7.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/SI06_H1/H7.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15_H1/E4.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15_H1/F3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15_H1/G3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15_H1/E3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15_H1/H3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/MI15_H1/F4.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13_FluB/G1.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13_FluB/F1.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13_FluB/E1.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Phu13_FluB/H1.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40_FluB/H3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40_FluB/G3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40_FluB/F3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40_FluB/E3.xls</t>
+  </si>
+  <si>
+    <t>experimental_data/validation/BLI/oPool_competition_validation/Lee40_FluB/F5.xls</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
     <col min="3" max="3" width="49.33203125" customWidth="1"/>
-    <col min="4" max="4" width="57.83203125" customWidth="1"/>
+    <col min="4" max="4" width="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -677,7 +677,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -688,10 +688,10 @@
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -702,10 +702,10 @@
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -716,10 +716,10 @@
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,10 +730,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -744,10 +744,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -758,10 +758,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -772,10 +772,10 @@
         <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -786,10 +786,10 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -800,10 +800,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -814,10 +814,10 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -828,10 +828,10 @@
         <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -842,10 +842,10 @@
         <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -856,10 +856,10 @@
         <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -870,10 +870,10 @@
         <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -884,10 +884,10 @@
         <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -898,10 +898,10 @@
         <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -912,10 +912,10 @@
         <v>23</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -926,10 +926,10 @@
         <v>24</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -940,10 +940,10 @@
         <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -954,10 +954,10 @@
         <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -968,10 +968,10 @@
         <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -982,10 +982,10 @@
         <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -996,10 +996,10 @@
         <v>25</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1010,10 +1010,10 @@
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1024,10 +1024,10 @@
         <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1038,7 +1038,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>79</v>
